--- a/data/sample_khimik.xlsx
+++ b/data/sample_khimik.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C2" t="n">
         <v>5.6</v>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C3" t="n">
         <v>5.633</v>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C4" t="n">
         <v>5.591</v>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C5" t="n">
         <v>5.569</v>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C6" t="n">
         <v>5.617</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C7" t="n">
         <v>5.627</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C8" t="n">
         <v>2.111</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C9" t="n">
         <v>2.105</v>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C10" t="n">
         <v>2.088</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C11" t="n">
         <v>2.098</v>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C12" t="n">
         <v>2.113</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C13" t="n">
         <v>2.099</v>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C14" t="n">
         <v>2.313</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C15" t="n">
         <v>2.293</v>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C16" t="n">
         <v>2.289</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C17" t="n">
         <v>2.31</v>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C18" t="n">
         <v>2.308</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C19" t="n">
         <v>2.288</v>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C20" t="n">
         <v>3.503</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C21" t="n">
         <v>3.479</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C22" t="n">
         <v>3.502</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C23" t="n">
         <v>3.52</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C24" t="n">
         <v>3.492</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C25" t="n">
         <v>3.482</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C26" t="n">
         <v>2.19</v>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C27" t="n">
         <v>2.193</v>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C28" t="n">
         <v>2.212</v>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C29" t="n">
         <v>2.204</v>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C30" t="n">
         <v>2.187</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C31" t="n">
         <v>2.199</v>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C32" t="n">
         <v>1.889</v>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C33" t="n">
         <v>1.905</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C34" t="n">
         <v>1.91</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C35" t="n">
         <v>1.893</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C36" t="n">
         <v>1.892</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C37" t="n">
         <v>1.909</v>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C38" t="n">
         <v>1.797</v>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C39" t="n">
         <v>1.811</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C40" t="n">
         <v>1.8</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C41" t="n">
         <v>1.789</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C42" t="n">
         <v>1.803</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C43" t="n">
         <v>1.81</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C44" t="n">
         <v>3.413</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C45" t="n">
         <v>3.414</v>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C46" t="n">
         <v>3.383</v>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C47" t="n">
         <v>3.391</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C48" t="n">
         <v>3.419</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C49" t="n">
         <v>3.404</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C50" t="n">
         <v>1.71</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C51" t="n">
         <v>1.697</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C52" t="n">
         <v>1.691</v>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C53" t="n">
         <v>1.705</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C54" t="n">
         <v>1.708</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C55" t="n">
         <v>1.693</v>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46281.4375</v>
+        <v>46282.4375</v>
       </c>
       <c r="C56" t="n">
         <v>1.604</v>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>46286.4375</v>
+        <v>46287.4375</v>
       </c>
       <c r="C57" t="n">
         <v>1.591</v>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46291.4375</v>
+        <v>46292.4375</v>
       </c>
       <c r="C58" t="n">
         <v>1.598</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="C59" t="n">
         <v>1.61</v>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46301.4375</v>
+        <v>46302.4375</v>
       </c>
       <c r="C60" t="n">
         <v>1.599</v>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>46306.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="C61" t="n">
         <v>1.591</v>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46236.4375</v>
+        <v>46237.4375</v>
       </c>
       <c r="C62" t="n">
         <v>1.395</v>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46241.4375</v>
+        <v>46242.4375</v>
       </c>
       <c r="C63" t="n">
         <v>1.394</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46246.4375</v>
+        <v>46247.4375</v>
       </c>
       <c r="C64" t="n">
         <v>1.406</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>46251.4375</v>
+        <v>46252.4375</v>
       </c>
       <c r="C65" t="n">
         <v>1.405</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>46256.4375</v>
+        <v>46257.4375</v>
       </c>
       <c r="C66" t="n">
         <v>1.393</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>46261.4375</v>
+        <v>46262.4375</v>
       </c>
       <c r="C67" t="n">
         <v>1.397</v>
@@ -2470,6 +2470,186 @@
       </c>
       <c r="H67" t="n">
         <v>300</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>46282.4375</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3.609</v>
+      </c>
+      <c r="D68" t="n">
+        <v>32190</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>46287.4375</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3.618</v>
+      </c>
+      <c r="D69" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>46292.4375</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3.586</v>
+      </c>
+      <c r="D70" t="n">
+        <v>31810</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>46297.4375</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3.585</v>
+      </c>
+      <c r="D71" t="n">
+        <v>32050</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>46302.4375</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3.618</v>
+      </c>
+      <c r="D72" t="n">
+        <v>32180</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>46307.4375</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="D73" t="n">
+        <v>31910</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" t="n">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
